--- a/GOOS_EOV_Administrative_Info.xlsx
+++ b/GOOS_EOV_Administrative_Info.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10116"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jebyrnes/Library/CloudStorage/GoogleDrive-jarrett.byrnes@gmail.com/.shortcut-targets-by-id/1uNfJ83WmlmCErHo4iUjWr1UYx8ZEmsih/Macroalgal EOV Data Processing docs/SOP_Visual/goos_data_sheets_and_entry_forms/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4475CEA9-7FB2-6042-9609-D9F763C0014E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2600148-B420-734F-9122-C67D177FF0A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3860" yWindow="500" windowWidth="27640" windowHeight="16940" xr2:uid="{3BB4A0A6-1544-394D-83A2-653BD8DB631A}"/>
+    <workbookView xWindow="5940" yWindow="1620" windowWidth="27660" windowHeight="16960" xr2:uid="{3BB4A0A6-1544-394D-83A2-653BD8DB631A}"/>
   </bookViews>
   <sheets>
-    <sheet name="Organization Info" sheetId="1" r:id="rId1"/>
-    <sheet name="Observer Info" sheetId="3" r:id="rId2"/>
-    <sheet name="Metadata" sheetId="2" r:id="rId3"/>
+    <sheet name="Dataset Info" sheetId="4" r:id="rId1"/>
+    <sheet name="Organization Info" sheetId="1" r:id="rId2"/>
+    <sheet name="Observer Info" sheetId="3" r:id="rId3"/>
+    <sheet name="Metadata" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="46">
   <si>
     <t>Organisation</t>
   </si>
@@ -125,13 +126,64 @@
   </si>
   <si>
     <t>Data Contact email</t>
+  </si>
+  <si>
+    <t>Dataset title</t>
+  </si>
+  <si>
+    <t>Shortname</t>
+  </si>
+  <si>
+    <t>License</t>
+  </si>
+  <si>
+    <t>Update frequency</t>
+  </si>
+  <si>
+    <t>Keywords</t>
+  </si>
+  <si>
+    <t>Link to dataset if elsewhere</t>
+  </si>
+  <si>
+    <t>Sample Area WKT</t>
+  </si>
+  <si>
+    <t>Standard name of license for data distribution (e.g. CC0, CC-BY, CC-BY-NC)</t>
+  </si>
+  <si>
+    <t>URL of location where dataset can be found outside of OBIS if it exists. This field is optional. It should include the full URL, including http://</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The frequency with which changes are made to the dataset after its initial deposition. </t>
+  </si>
+  <si>
+    <t>Keyword Thesaurus</t>
+  </si>
+  <si>
+    <t>URL to the location of the standardized vocabulary for keywords</t>
+  </si>
+  <si>
+    <t>Comma separated keywords describing the content of the data set using a standardized vocabulary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A unique "shortname" that is at least three characters in length, may contain alphanumeric characters (A-Z, a-z and 0-9), but must not contain white space, punctuation other than hyphens or underscores, or accented characters (e.g., "firstresource" or "first_resource", but not "first resource" or "première ressource!"). </t>
+  </si>
+  <si>
+    <t>The full name of the data set.</t>
+  </si>
+  <si>
+    <t>A textual description of the dataset. What is it? Why was it created? What does it contain? Consider this an abstract.</t>
+  </si>
+  <si>
+    <t>The boundaries of the total area sampled in well-known text. See  OGC 06-103r4 for the standard. If not included, will be inferred from the data.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -183,6 +235,13 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -204,7 +263,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -221,6 +280,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -239,9 +299,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -279,7 +339,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -385,7 +445,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -527,13 +587,64 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C39FD86-E641-AA4F-BA8C-80D5AE8708CF}">
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="17" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="37.5" style="7" customWidth="1"/>
+    <col min="2" max="2" width="24" style="7" customWidth="1"/>
+    <col min="3" max="3" width="9.1640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.33203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="29.83203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20" style="7" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="10.83203125" style="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BACB5F4-A3AB-E341-AE55-5B3792E26FCF}">
   <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -573,7 +684,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B4F1247-002D-9A4D-A2A0-47E335E9D3FE}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -609,9 +720,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6635EC42-3C58-AF48-8516-B9323009F78E}">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="25.1640625" customWidth="1"/>
@@ -634,131 +745,238 @@
     </row>
     <row r="2" spans="1:4" ht="18" x14ac:dyDescent="0.2">
       <c r="A2" s="7" t="s">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="1"/>
-    </row>
-    <row r="3" spans="1:4" ht="54" x14ac:dyDescent="0.2">
+      <c r="D2" s="6"/>
+    </row>
+    <row r="3" spans="1:4" ht="90" x14ac:dyDescent="0.2">
       <c r="A3" s="7" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>5</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D3" s="6"/>
     </row>
     <row r="4" spans="1:4" ht="36" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="6"/>
+    </row>
+    <row r="5" spans="1:4" ht="36" x14ac:dyDescent="0.2">
+      <c r="A5" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" s="6"/>
+    </row>
+    <row r="6" spans="1:4" ht="36" x14ac:dyDescent="0.2">
+      <c r="A6" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="6"/>
+    </row>
+    <row r="7" spans="1:4" ht="36" x14ac:dyDescent="0.2">
+      <c r="A7" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" s="6"/>
+    </row>
+    <row r="8" spans="1:4" ht="18" x14ac:dyDescent="0.2">
+      <c r="A8" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" s="1"/>
+      <c r="D8" s="6"/>
+    </row>
+    <row r="9" spans="1:4" ht="54" x14ac:dyDescent="0.2">
+      <c r="A9" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D9" s="6"/>
+    </row>
+    <row r="10" spans="1:4" ht="54" x14ac:dyDescent="0.2">
+      <c r="A10" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D10" s="6"/>
+    </row>
+    <row r="11" spans="1:4" ht="18" x14ac:dyDescent="0.2">
+      <c r="A11" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D11" s="1"/>
+    </row>
+    <row r="12" spans="1:4" ht="54" x14ac:dyDescent="0.2">
+      <c r="A12" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="36" x14ac:dyDescent="0.2">
+      <c r="A13" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B13" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" s="1"/>
-    </row>
-    <row r="5" spans="1:4" ht="18" x14ac:dyDescent="0.2">
-      <c r="A5" s="7" t="s">
+      <c r="C13" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D13" s="1"/>
+    </row>
+    <row r="14" spans="1:4" ht="18" x14ac:dyDescent="0.2">
+      <c r="A14" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B14" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D5" s="1"/>
-    </row>
-    <row r="6" spans="1:4" ht="18" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
+      <c r="C14" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D14" s="1"/>
+    </row>
+    <row r="15" spans="1:4" ht="18" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B15" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D6" s="1"/>
-    </row>
-    <row r="7" spans="1:4" ht="36" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
+      <c r="C15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D15" s="1"/>
+    </row>
+    <row r="16" spans="1:4" ht="36" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B16" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D7" s="1"/>
-    </row>
-    <row r="8" spans="1:4" ht="54" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
+      <c r="C16" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" s="1"/>
+    </row>
+    <row r="17" spans="1:4" ht="54" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B17" s="9" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="36" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
+    <row r="18" spans="1:4" ht="36" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B18" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D9" s="1"/>
-    </row>
-    <row r="10" spans="1:4" ht="18" x14ac:dyDescent="0.2">
-      <c r="A10" s="1" t="s">
+      <c r="C18" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D18" s="1"/>
+    </row>
+    <row r="19" spans="1:4" ht="18" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B19" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D10" s="1"/>
-    </row>
-    <row r="11" spans="1:4" ht="54" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
+      <c r="C19" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D19" s="1"/>
+    </row>
+    <row r="20" spans="1:4" ht="54" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B20" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C20" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="36" x14ac:dyDescent="0.2">
-      <c r="A12" s="1" t="s">
+    <row r="21" spans="1:4" ht="36" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B21" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D12" s="1"/>
+      <c r="C21" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D21" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>